--- a/dashboard_september_injected.xlsx
+++ b/dashboard_september_injected.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="_-[$Rp]* #,##0.00_-;\-[$Rp]* #,##0.00_-;_-[$Rp]* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -177,6 +177,14 @@
       <family val="2"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002563EB"/>
     </font>
   </fonts>
   <fills count="14">
@@ -639,7 +647,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -914,6 +922,12 @@
     </xf>
     <xf numFmtId="165" fontId="20" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -24073,18 +24087,13 @@
       <c r="I15" s="119" t="n"/>
       <c r="J15" s="119" t="n"/>
       <c r="K15" s="119" t="n"/>
-      <c r="L15" s="19">
-        <f>IF(SUM(G15:K15)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M15" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N15" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L15" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M15" s="119" t="n"/>
+      <c r="N15" s="22" t="n"/>
       <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n"/>
       <c r="Q15" s="42" t="n">
@@ -28305,18 +28314,13 @@
       <c r="I87" s="119" t="n"/>
       <c r="J87" s="119" t="n"/>
       <c r="K87" s="119" t="n"/>
-      <c r="L87" s="19">
-        <f>IF(SUM(G87:K87)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M87" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N87" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L87" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M87" s="119" t="n"/>
+      <c r="N87" s="22" t="n"/>
       <c r="O87" s="6" t="n"/>
       <c r="P87" s="6" t="n"/>
       <c r="Q87" s="42" t="n">
@@ -33419,18 +33423,13 @@
       <c r="I215" s="119" t="n"/>
       <c r="J215" s="119" t="n"/>
       <c r="K215" s="119" t="n"/>
-      <c r="L215" s="19">
-        <f>IF(SUM(G215:K215)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M215" s="119" t="n">
-        <v>75000</v>
-      </c>
-      <c r="N215" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L215" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M215" s="119" t="n"/>
+      <c r="N215" s="22" t="n"/>
       <c r="O215" s="6" t="n"/>
       <c r="P215" s="6" t="n"/>
       <c r="Q215" s="6" t="n"/>
@@ -34473,9 +34472,10 @@
       <c r="I242" s="119" t="n"/>
       <c r="J242" s="119" t="n"/>
       <c r="K242" s="119" t="n"/>
-      <c r="L242" s="19">
-        <f>IF(SUM(G242:K242)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
+      <c r="L242" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
       </c>
       <c r="M242" s="119" t="n"/>
       <c r="N242" s="22" t="n"/>
@@ -40457,18 +40457,13 @@
       <c r="I397" s="119" t="n"/>
       <c r="J397" s="119" t="n"/>
       <c r="K397" s="119" t="n"/>
-      <c r="L397" s="19">
-        <f>IF(SUM(G397:K397)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M397" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N397" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L397" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M397" s="119" t="n"/>
+      <c r="N397" s="22" t="n"/>
       <c r="O397" s="6" t="n"/>
       <c r="P397" s="6" t="n"/>
       <c r="Q397" s="6" t="n"/>
@@ -41325,18 +41320,13 @@
       <c r="I419" s="119" t="n"/>
       <c r="J419" s="119" t="n"/>
       <c r="K419" s="119" t="n"/>
-      <c r="L419" s="19">
-        <f>IF(SUM(G419:K419)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M419" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N419" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L419" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M419" s="119" t="n"/>
+      <c r="N419" s="22" t="n"/>
       <c r="O419" s="6" t="n"/>
       <c r="P419" s="6" t="n"/>
       <c r="Q419" s="6" t="n"/>
@@ -41489,18 +41479,13 @@
       <c r="I423" s="119" t="n"/>
       <c r="J423" s="119" t="n"/>
       <c r="K423" s="119" t="n"/>
-      <c r="L423" s="19">
-        <f>IF(SUM(G423:K423)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M423" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N423" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L423" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M423" s="119" t="n"/>
+      <c r="N423" s="22" t="n"/>
       <c r="O423" s="6" t="n"/>
       <c r="P423" s="6" t="n"/>
       <c r="Q423" s="6" t="n"/>
@@ -42627,18 +42612,13 @@
       <c r="I452" s="119" t="n"/>
       <c r="J452" s="119" t="n"/>
       <c r="K452" s="119" t="n"/>
-      <c r="L452" s="19">
-        <f>IF(SUM(G452:K452)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M452" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N452" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L452" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M452" s="119" t="n"/>
+      <c r="N452" s="22" t="n"/>
       <c r="O452" s="6" t="n"/>
       <c r="P452" s="6" t="n"/>
       <c r="Q452" s="6" t="n"/>
@@ -42821,18 +42801,13 @@
       <c r="I457" s="119" t="n"/>
       <c r="J457" s="119" t="n"/>
       <c r="K457" s="119" t="n"/>
-      <c r="L457" s="19">
-        <f>IF(SUM(G457:K457)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M457" s="119" t="n">
-        <v>75000</v>
-      </c>
-      <c r="N457" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L457" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M457" s="119" t="n"/>
+      <c r="N457" s="22" t="n"/>
       <c r="O457" s="6" t="n"/>
       <c r="P457" s="6" t="n"/>
       <c r="Q457" s="6" t="n"/>
@@ -43423,18 +43398,13 @@
       <c r="I472" s="119" t="n"/>
       <c r="J472" s="119" t="n"/>
       <c r="K472" s="119" t="n"/>
-      <c r="L472" s="19">
-        <f>IF(SUM(G472:K472)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M472" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N472" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L472" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M472" s="119" t="n"/>
+      <c r="N472" s="22" t="n"/>
       <c r="O472" s="6" t="n"/>
       <c r="P472" s="6" t="n"/>
       <c r="Q472" s="6" t="n"/>
@@ -45287,18 +45257,13 @@
       <c r="I520" s="119" t="n"/>
       <c r="J520" s="119" t="n"/>
       <c r="K520" s="119" t="n"/>
-      <c r="L520" s="19">
-        <f>IF(SUM(G520:K520)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M520" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N520" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L520" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M520" s="119" t="n"/>
+      <c r="N520" s="22" t="n"/>
       <c r="O520" s="6" t="n"/>
       <c r="P520" s="6" t="n"/>
       <c r="Q520" s="6" t="n"/>
@@ -45329,18 +45294,13 @@
       <c r="I521" s="119" t="n"/>
       <c r="J521" s="119" t="n"/>
       <c r="K521" s="119" t="n"/>
-      <c r="L521" s="19">
-        <f>IF(SUM(G521:K521)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M521" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N521" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L521" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M521" s="119" t="n"/>
+      <c r="N521" s="22" t="n"/>
       <c r="O521" s="6" t="n"/>
       <c r="P521" s="6" t="n"/>
       <c r="Q521" s="6" t="n"/>
@@ -54207,7 +54167,7 @@
           <t>URAIAN</t>
         </is>
       </c>
-      <c r="E2" s="122" t="inlineStr">
+      <c r="E2" s="124" t="inlineStr">
         <is>
           <t>JUMLAH</t>
         </is>
@@ -54234,10 +54194,10 @@
           <t>fee mas fany</t>
         </is>
       </c>
-      <c r="E3" s="123" t="n">
+      <c r="E3" s="125" t="n">
         <v>65000</v>
       </c>
-      <c r="F3" s="123">
+      <c r="F3" s="125">
         <f>SUM(E3:E93)</f>
         <v/>
       </c>
@@ -54258,10 +54218,10 @@
           <t>fee mba ida</t>
         </is>
       </c>
-      <c r="E4" s="123" t="n">
+      <c r="E4" s="125" t="n">
         <v>510000</v>
       </c>
-      <c r="F4" s="123" t="n"/>
+      <c r="F4" s="125" t="n"/>
       <c r="G4" s="6" t="n"/>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="77">
@@ -54279,10 +54239,10 @@
           <t>fee mba dita</t>
         </is>
       </c>
-      <c r="E5" s="123" t="n">
+      <c r="E5" s="125" t="n">
         <v>235000</v>
       </c>
-      <c r="F5" s="123" t="n"/>
+      <c r="F5" s="125" t="n"/>
       <c r="G5" s="6" t="n"/>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="77">
@@ -54300,10 +54260,10 @@
           <t>fee mas fany</t>
         </is>
       </c>
-      <c r="E6" s="123" t="n">
+      <c r="E6" s="125" t="n">
         <v>100000</v>
       </c>
-      <c r="F6" s="123" t="n"/>
+      <c r="F6" s="125" t="n"/>
       <c r="G6" s="6" t="n"/>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="77">
@@ -54321,10 +54281,10 @@
           <t>fee mba dita</t>
         </is>
       </c>
-      <c r="E7" s="123" t="n">
+      <c r="E7" s="125" t="n">
         <v>85000</v>
       </c>
-      <c r="F7" s="123" t="n"/>
+      <c r="F7" s="125" t="n"/>
       <c r="G7" s="6" t="n"/>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="77">
@@ -54342,10 +54302,10 @@
           <t>fee mba yeni</t>
         </is>
       </c>
-      <c r="E8" s="123" t="n">
+      <c r="E8" s="125" t="n">
         <v>60000</v>
       </c>
-      <c r="F8" s="123" t="n"/>
+      <c r="F8" s="125" t="n"/>
       <c r="G8" s="6" t="n"/>
     </row>
     <row r="9" ht="12.75" customHeight="1" s="77">
@@ -54363,10 +54323,10 @@
           <t>fee mba lili</t>
         </is>
       </c>
-      <c r="E9" s="123" t="n">
+      <c r="E9" s="125" t="n">
         <v>230000</v>
       </c>
-      <c r="F9" s="123" t="n"/>
+      <c r="F9" s="125" t="n"/>
       <c r="G9" s="6" t="n"/>
     </row>
     <row r="10" ht="12.75" customHeight="1" s="77">
@@ -54384,10 +54344,10 @@
           <t>fee mas fany</t>
         </is>
       </c>
-      <c r="E10" s="123" t="n">
+      <c r="E10" s="125" t="n">
         <v>195000</v>
       </c>
-      <c r="F10" s="123" t="n"/>
+      <c r="F10" s="125" t="n"/>
       <c r="G10" s="6" t="n"/>
     </row>
     <row r="11" ht="12.75" customHeight="1" s="77">
@@ -54405,10 +54365,10 @@
           <t>fee mas fany</t>
         </is>
       </c>
-      <c r="E11" s="123" t="n">
+      <c r="E11" s="125" t="n">
         <v>50000</v>
       </c>
-      <c r="F11" s="123" t="n"/>
+      <c r="F11" s="125" t="n"/>
       <c r="G11" s="6" t="n"/>
     </row>
     <row r="12" ht="12.75" customHeight="1" s="77">
@@ -54426,10 +54386,10 @@
           <t>fee mas fany</t>
         </is>
       </c>
-      <c r="E12" s="123" t="n">
+      <c r="E12" s="125" t="n">
         <v>50000</v>
       </c>
-      <c r="F12" s="123" t="n"/>
+      <c r="F12" s="125" t="n"/>
       <c r="G12" s="6" t="n"/>
     </row>
     <row r="13" ht="12.75" customHeight="1" s="77">
@@ -54437,7 +54397,7 @@
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="42" t="n"/>
       <c r="D13" s="42" t="n"/>
-      <c r="E13" s="123" t="n"/>
+      <c r="E13" s="125" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
     </row>
@@ -54446,7 +54406,7 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="42" t="n"/>
       <c r="D14" s="42" t="n"/>
-      <c r="E14" s="123" t="n"/>
+      <c r="E14" s="125" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
     </row>
@@ -54455,7 +54415,7 @@
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="42" t="n"/>
       <c r="D15" s="42" t="n"/>
-      <c r="E15" s="123" t="n"/>
+      <c r="E15" s="125" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
     </row>
@@ -54464,7 +54424,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="42" t="n"/>
       <c r="D16" s="42" t="n"/>
-      <c r="E16" s="123" t="n"/>
+      <c r="E16" s="125" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
     </row>
@@ -54473,7 +54433,7 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="42" t="n"/>
       <c r="D17" s="42" t="n"/>
-      <c r="E17" s="123" t="n"/>
+      <c r="E17" s="125" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
     </row>
@@ -54482,7 +54442,7 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="42" t="n"/>
       <c r="D18" s="42" t="n"/>
-      <c r="E18" s="123" t="n"/>
+      <c r="E18" s="125" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
     </row>
@@ -54491,7 +54451,7 @@
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="42" t="n"/>
       <c r="D19" s="42" t="n"/>
-      <c r="E19" s="123" t="n"/>
+      <c r="E19" s="125" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
     </row>
@@ -54500,7 +54460,7 @@
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="42" t="n"/>
       <c r="D20" s="42" t="n"/>
-      <c r="E20" s="123" t="n"/>
+      <c r="E20" s="125" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
     </row>
@@ -54509,7 +54469,7 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="42" t="n"/>
       <c r="D21" s="42" t="n"/>
-      <c r="E21" s="123" t="n"/>
+      <c r="E21" s="125" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
     </row>
@@ -54518,7 +54478,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="42" t="n"/>
       <c r="D22" s="42" t="n"/>
-      <c r="E22" s="123" t="n"/>
+      <c r="E22" s="125" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
     </row>
@@ -54527,7 +54487,7 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="42" t="n"/>
       <c r="D23" s="42" t="n"/>
-      <c r="E23" s="123" t="n"/>
+      <c r="E23" s="125" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
     </row>
@@ -54536,7 +54496,7 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="42" t="n"/>
       <c r="D24" s="42" t="n"/>
-      <c r="E24" s="123" t="n"/>
+      <c r="E24" s="125" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
     </row>
@@ -54545,7 +54505,7 @@
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="42" t="n"/>
       <c r="D25" s="42" t="n"/>
-      <c r="E25" s="123" t="n"/>
+      <c r="E25" s="125" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
     </row>
@@ -54554,7 +54514,7 @@
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="42" t="n"/>
       <c r="D26" s="42" t="n"/>
-      <c r="E26" s="123" t="n"/>
+      <c r="E26" s="125" t="n"/>
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="6" t="n"/>
     </row>
@@ -63307,7 +63267,7 @@
           <t>PAKET</t>
         </is>
       </c>
-      <c r="D2" s="124" t="inlineStr">
+      <c r="D2" s="126" t="inlineStr">
         <is>
           <t>HARGA</t>
         </is>
@@ -63324,7 +63284,7 @@
           <t>5mbps</t>
         </is>
       </c>
-      <c r="D3" s="125" t="n">
+      <c r="D3" s="127" t="n">
         <v>50000</v>
       </c>
       <c r="E3" s="6" t="n"/>
@@ -63339,7 +63299,7 @@
           <t>7mbps</t>
         </is>
       </c>
-      <c r="D4" s="125" t="n">
+      <c r="D4" s="127" t="n">
         <v>75000</v>
       </c>
       <c r="E4" s="6" t="n"/>
@@ -63354,7 +63314,7 @@
           <t>9mbps</t>
         </is>
       </c>
-      <c r="D5" s="125" t="n">
+      <c r="D5" s="127" t="n">
         <v>90000</v>
       </c>
       <c r="E5" s="6" t="n"/>
@@ -63369,7 +63329,7 @@
           <t>10mbps</t>
         </is>
       </c>
-      <c r="D6" s="125" t="n">
+      <c r="D6" s="127" t="n">
         <v>100000</v>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -63384,7 +63344,7 @@
           <t>15mbps</t>
         </is>
       </c>
-      <c r="D7" s="125" t="n">
+      <c r="D7" s="127" t="n">
         <v>150000</v>
       </c>
       <c r="E7" s="6" t="n"/>
@@ -63399,7 +63359,7 @@
           <t>20mbps</t>
         </is>
       </c>
-      <c r="D8" s="125" t="n">
+      <c r="D8" s="127" t="n">
         <v>200000</v>
       </c>
       <c r="E8" s="6" t="n"/>
@@ -63414,7 +63374,7 @@
           <t>30mbps</t>
         </is>
       </c>
-      <c r="D9" s="125" t="n">
+      <c r="D9" s="127" t="n">
         <v>250000</v>
       </c>
       <c r="E9" s="6" t="n"/>
@@ -63429,7 +63389,7 @@
           <t>50mbps</t>
         </is>
       </c>
-      <c r="D10" s="125" t="n">
+      <c r="D10" s="127" t="n">
         <v>350000</v>
       </c>
       <c r="E10" s="6" t="n"/>
@@ -63444,7 +63404,7 @@
           <t>100mbps</t>
         </is>
       </c>
-      <c r="D11" s="125" t="n">
+      <c r="D11" s="127" t="n">
         <v>1850000</v>
       </c>
       <c r="E11" s="6" t="n"/>
@@ -63459,7 +63419,7 @@
           <t>200Mbps</t>
         </is>
       </c>
-      <c r="D12" s="125" t="n">
+      <c r="D12" s="127" t="n">
         <v>3700000</v>
       </c>
       <c r="E12" s="6" t="n"/>
@@ -63474,7 +63434,7 @@
           <t>300Mbps</t>
         </is>
       </c>
-      <c r="D13" s="125" t="n">
+      <c r="D13" s="127" t="n">
         <v>5550000</v>
       </c>
       <c r="E13" s="6" t="n"/>
@@ -63489,7 +63449,7 @@
           <t>400Mbps</t>
         </is>
       </c>
-      <c r="D14" s="125" t="n">
+      <c r="D14" s="127" t="n">
         <v>7400000</v>
       </c>
       <c r="E14" s="6" t="n"/>
@@ -63504,7 +63464,7 @@
           <t>500Mbps</t>
         </is>
       </c>
-      <c r="D15" s="125" t="n">
+      <c r="D15" s="127" t="n">
         <v>9250000</v>
       </c>
       <c r="E15" s="6" t="n"/>
@@ -63519,7 +63479,7 @@
           <t>600Mbps</t>
         </is>
       </c>
-      <c r="D16" s="125" t="n">
+      <c r="D16" s="127" t="n">
         <v>11100000</v>
       </c>
       <c r="E16" s="6" t="n"/>

--- a/dashboard_september_injected.xlsx
+++ b/dashboard_september_injected.xlsx
@@ -33455,7 +33455,9 @@
         <f>NamaPelanggan!H215</f>
         <v/>
       </c>
-      <c r="G216" s="119" t="n"/>
+      <c r="G216" s="119" t="n">
+        <v>100000</v>
+      </c>
       <c r="H216" s="119" t="n"/>
       <c r="I216" s="119" t="n"/>
       <c r="J216" s="119" t="n"/>
@@ -33464,14 +33466,8 @@
         <f>IF(SUM(G216:K216)&gt;0,"LUNAS","BELUM LUNAS")</f>
         <v/>
       </c>
-      <c r="M216" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N216" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="M216" s="119" t="n"/>
+      <c r="N216" s="22" t="n"/>
       <c r="O216" s="6" t="n"/>
       <c r="P216" s="6" t="n"/>
       <c r="Q216" s="6" t="n"/>

--- a/dashboard_september_injected.xlsx
+++ b/dashboard_september_injected.xlsx
@@ -35493,18 +35493,13 @@
       <c r="I269" s="119" t="n"/>
       <c r="J269" s="119" t="n"/>
       <c r="K269" s="119" t="n"/>
-      <c r="L269" s="19">
-        <f>IF(SUM(G269:K269)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M269" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N269" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L269" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M269" s="119" t="n"/>
+      <c r="N269" s="22" t="n"/>
       <c r="O269" s="6" t="n"/>
       <c r="P269" s="6" t="n"/>
       <c r="Q269" s="6" t="n"/>
@@ -35801,18 +35796,13 @@
       <c r="I277" s="119" t="n"/>
       <c r="J277" s="119" t="n"/>
       <c r="K277" s="119" t="n"/>
-      <c r="L277" s="19">
-        <f>IF(SUM(G277:K277)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M277" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N277" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L277" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M277" s="119" t="n"/>
+      <c r="N277" s="22" t="n"/>
       <c r="O277" s="6" t="n"/>
       <c r="P277" s="6" t="n"/>
       <c r="Q277" s="6" t="n"/>
@@ -37273,18 +37263,13 @@
       <c r="I315" s="119" t="n"/>
       <c r="J315" s="119" t="n"/>
       <c r="K315" s="119" t="n"/>
-      <c r="L315" s="19">
-        <f>IF(SUM(G315:K315)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M315" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N315" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L315" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M315" s="119" t="n"/>
+      <c r="N315" s="22" t="n"/>
       <c r="O315" s="6" t="n"/>
       <c r="P315" s="6" t="n"/>
       <c r="Q315" s="6" t="n"/>
@@ -37737,18 +37722,13 @@
       <c r="I327" s="119" t="n"/>
       <c r="J327" s="119" t="n"/>
       <c r="K327" s="119" t="n"/>
-      <c r="L327" s="19">
-        <f>IF(SUM(G327:K327)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M327" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N327" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L327" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M327" s="119" t="n"/>
+      <c r="N327" s="22" t="n"/>
       <c r="O327" s="6" t="n"/>
       <c r="P327" s="6" t="n"/>
       <c r="Q327" s="6" t="n"/>
@@ -39265,18 +39245,13 @@
       <c r="I367" s="119" t="n"/>
       <c r="J367" s="119" t="n"/>
       <c r="K367" s="119" t="n"/>
-      <c r="L367" s="19">
-        <f>IF(SUM(G367:K367)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M367" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N367" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L367" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M367" s="119" t="n"/>
+      <c r="N367" s="22" t="n"/>
       <c r="O367" s="6" t="n"/>
       <c r="P367" s="6" t="n"/>
       <c r="Q367" s="6" t="n"/>
@@ -39615,18 +39590,13 @@
       <c r="I376" s="119" t="n"/>
       <c r="J376" s="119" t="n"/>
       <c r="K376" s="119" t="n"/>
-      <c r="L376" s="19">
-        <f>IF(SUM(G376:K376)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M376" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N376" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L376" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M376" s="119" t="n"/>
+      <c r="N376" s="22" t="n"/>
       <c r="O376" s="6" t="n"/>
       <c r="P376" s="6" t="n"/>
       <c r="Q376" s="6" t="n"/>
@@ -39657,18 +39627,13 @@
       <c r="I377" s="119" t="n"/>
       <c r="J377" s="119" t="n"/>
       <c r="K377" s="119" t="n"/>
-      <c r="L377" s="19">
-        <f>IF(SUM(G377:K377)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M377" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N377" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L377" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M377" s="119" t="n"/>
+      <c r="N377" s="22" t="n"/>
       <c r="O377" s="6" t="n"/>
       <c r="P377" s="6" t="n"/>
       <c r="Q377" s="6" t="n"/>
@@ -39779,18 +39744,13 @@
       <c r="I380" s="119" t="n"/>
       <c r="J380" s="119" t="n"/>
       <c r="K380" s="119" t="n"/>
-      <c r="L380" s="19">
-        <f>IF(SUM(G380:K380)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M380" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N380" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L380" s="122" t="inlineStr">
+        <is>
+          <t>SUDAH OFF</t>
+        </is>
+      </c>
+      <c r="M380" s="119" t="n"/>
+      <c r="N380" s="22" t="n"/>
       <c r="O380" s="6" t="n"/>
       <c r="P380" s="6" t="n"/>
       <c r="Q380" s="6" t="n"/>
@@ -43078,18 +43038,13 @@
       <c r="I464" s="119" t="n"/>
       <c r="J464" s="119" t="n"/>
       <c r="K464" s="119" t="n"/>
-      <c r="L464" s="19">
-        <f>IF(SUM(G464:K464)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M464" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N464" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L464" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M464" s="119" t="n"/>
+      <c r="N464" s="22" t="n"/>
       <c r="O464" s="6" t="n"/>
       <c r="P464" s="6" t="n"/>
       <c r="Q464" s="6" t="n"/>

--- a/dashboard_september_injected.xlsx
+++ b/dashboard_september_injected.xlsx
@@ -33730,18 +33730,13 @@
       <c r="I223" s="119" t="n"/>
       <c r="J223" s="119" t="n"/>
       <c r="K223" s="119" t="n"/>
-      <c r="L223" s="19">
-        <f>IF(SUM(G223:K223)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M223" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N223" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L223" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M223" s="119" t="n"/>
+      <c r="N223" s="22" t="n"/>
       <c r="O223" s="6" t="n"/>
       <c r="P223" s="6" t="n"/>
       <c r="Q223" s="6" t="n"/>
@@ -33772,18 +33767,13 @@
       <c r="I224" s="119" t="n"/>
       <c r="J224" s="119" t="n"/>
       <c r="K224" s="119" t="n"/>
-      <c r="L224" s="19">
-        <f>IF(SUM(G224:K224)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M224" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N224" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L224" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M224" s="119" t="n"/>
+      <c r="N224" s="22" t="n"/>
       <c r="O224" s="6" t="n"/>
       <c r="P224" s="6" t="n"/>
       <c r="Q224" s="6" t="n"/>
@@ -33814,18 +33804,13 @@
       <c r="I225" s="119" t="n"/>
       <c r="J225" s="119" t="n"/>
       <c r="K225" s="119" t="n"/>
-      <c r="L225" s="19">
-        <f>IF(SUM(G225:K225)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M225" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N225" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L225" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M225" s="119" t="n"/>
+      <c r="N225" s="22" t="n"/>
       <c r="O225" s="6" t="n"/>
       <c r="P225" s="6" t="n"/>
       <c r="Q225" s="6" t="n"/>
@@ -33932,18 +33917,13 @@
       <c r="I228" s="119" t="n"/>
       <c r="J228" s="119" t="n"/>
       <c r="K228" s="119" t="n"/>
-      <c r="L228" s="19">
-        <f>IF(SUM(G228:K228)&gt;0,"LUNAS","BELUM LUNAS")</f>
-        <v/>
-      </c>
-      <c r="M228" s="119" t="n">
-        <v>100000</v>
-      </c>
-      <c r="N228" s="22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="L228" s="123" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="M228" s="119" t="n"/>
+      <c r="N228" s="22" t="n"/>
       <c r="O228" s="6" t="n"/>
       <c r="P228" s="6" t="n"/>
       <c r="Q228" s="6" t="n"/>
